--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,18 +16,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T12:43:55+05:30</t>
+    <t>Generated 2026-06-27T12:49:25+05:30</t>
   </si>
   <si>
     <t>Election method</t>
   </si>
   <si>
-    <t>none</t>
+    <t>github</t>
   </si>
   <si>
     <t>GitHub configured</t>
@@ -57,37 +57,37 @@
     <t>Mode / Role</t>
   </si>
   <si>
-    <t>SERVER (primary)</t>
+    <t>SERVER+LEADER (this instance is the GitHub primary)</t>
   </si>
   <si>
     <t>Self is leader</t>
   </si>
   <si>
+    <t>YES — this instance is the primary server</t>
+  </si>
+  <si>
+    <t>Current leader</t>
+  </si>
+  <si>
+    <t>Leader last update</t>
+  </si>
+  <si>
+    <t>2026-06-27T12:47:16+05:30 (2m9s ago)</t>
+  </si>
+  <si>
+    <t>Leader stale?</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Current leader</t>
-  </si>
-  <si>
-    <t>(no leader recorded)</t>
-  </si>
-  <si>
-    <t>Leader last update</t>
-  </si>
-  <si>
-    <t>(never)</t>
-  </si>
-  <si>
-    <t>Leader stale?</t>
-  </si>
-  <si>
     <t>Last check</t>
   </si>
   <si>
     <t>Check count</t>
   </si>
   <si>
-    <t>0</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -240,9 +240,6 @@
     <t>renewed</t>
   </si>
   <si>
-    <t>github</t>
-  </si>
-  <si>
     <t>2026-06-22T07:56:01.8822385+05:30</t>
   </si>
   <si>
@@ -342,10 +339,16 @@
     <t>12:31:38.887</t>
   </si>
   <si>
+    <t>2026-06-27T12:47:16.5293733+05:30</t>
+  </si>
+  <si>
+    <t>12:47:16.529</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T12:43:55+05:30</t>
+    <t>2026-06-27T12:49:25+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -945,7 +948,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-27 12:41:29</t>
+          <t>2026-06-27 12:47:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -955,12 +958,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-27 12:41:29</t>
+          <t>2026-06-27 12:47:00</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 33m 14s</t>
+          <t>73h 37m 39s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -970,7 +973,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>12:49:25</t>
         </is>
       </c>
     </row>
@@ -1027,17 +1030,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>389.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>60295.0</t>
+          <t>60287.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1047,7 +1050,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1062,12 +1065,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-27 12:41:29</t>
+          <t>2026-06-27 12:47:00</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>73h 31m 14s</t>
+          <t>73h 35m 39s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1077,7 +1080,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>12:49:25</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1199,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T12:31:38.8870316+05:30</t>
+          <t>2026-06-27T12:47:16.5293733+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1206,7 +1209,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12:31:38.887</t>
+          <t>12:47:16.529</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1530,23 +1533,23 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -1554,7 +1557,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -2176,7 +2179,7 @@
         <v>73</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>9</v>
@@ -2202,19 +2205,19 @@
         <v>16</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="F33" s="3" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>9</v>
@@ -2229,10 +2232,10 @@
         <v>9223372036</v>
       </c>
       <c r="K33" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L33" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="34">
@@ -2240,19 +2243,19 @@
         <v>17</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>9</v>
@@ -2267,10 +2270,10 @@
         <v>9223372036</v>
       </c>
       <c r="K34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L34" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="35">
@@ -2278,19 +2281,19 @@
         <v>18</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>9</v>
@@ -2305,10 +2308,10 @@
         <v>9223372036</v>
       </c>
       <c r="K35" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="36">
@@ -2316,19 +2319,19 @@
         <v>19</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>9</v>
@@ -2343,10 +2346,10 @@
         <v>9223372036</v>
       </c>
       <c r="K36" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="37">
@@ -2354,19 +2357,19 @@
         <v>20</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>9</v>
@@ -2381,10 +2384,10 @@
         <v>9223372036</v>
       </c>
       <c r="K37" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="38">
@@ -2392,19 +2395,19 @@
         <v>21</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>9</v>
@@ -2430,19 +2433,19 @@
         <v>22</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>9</v>
@@ -2457,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>44</v>
@@ -2468,19 +2471,19 @@
         <v>23</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="D40" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>9</v>
@@ -2506,19 +2509,19 @@
         <v>24</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>99</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>9</v>
@@ -2544,19 +2547,19 @@
         <v>25</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>9</v>
@@ -2582,19 +2585,19 @@
         <v>26</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>9</v>
@@ -2620,19 +2623,19 @@
         <v>27</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>9</v>
@@ -2658,19 +2661,19 @@
         <v>28</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>9</v>
@@ -2691,18 +2694,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="s">
+    <row r="46">
+      <c r="A46" s="4">
+        <v>29</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B47" t="s">
+      <c r="E46" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J46" s="4">
+        <v>0</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
         <v>109</v>
       </c>
-      <c r="D47" t="s">
+      <c r="B48" t="s">
         <v>110</v>
       </c>
-      <c r="E47">
-        <v>28</v>
+      <c r="D48" t="s">
+        <v>111</v>
+      </c>
+      <c r="E48">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T12:49:25+05:30</t>
+    <t>Generated 2026-06-27T12:56:55+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T12:47:16+05:30 (2m9s ago)</t>
+    <t>2026-06-27T12:54:54+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>Last error</t>
@@ -345,10 +345,22 @@
     <t>12:47:16.529</t>
   </si>
   <si>
+    <t>2026-06-27T12:52:26.7842306+05:30</t>
+  </si>
+  <si>
+    <t>12:52:26.784</t>
+  </si>
+  <si>
+    <t>2026-06-27T12:54:54.6924037+05:30</t>
+  </si>
+  <si>
+    <t>12:54:54.692</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T12:49:25+05:30</t>
+    <t>2026-06-27T12:56:55+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -943,7 +955,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 25s</t>
+          <t>0h 9m 54s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -963,7 +975,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 37m 39s</t>
+          <t>73h 42m 24s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -973,7 +985,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>12:49:25</t>
+          <t>12:56:55</t>
         </is>
       </c>
     </row>
@@ -1030,17 +1042,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>948.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>60287.0</t>
+          <t>60275.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1050,7 +1062,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>474</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1070,7 +1082,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>73h 35m 39s</t>
+          <t>73h 40m 34s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1080,7 +1092,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>12:49:25</t>
+          <t>12:56:55</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T12:47:16.5293733+05:30</t>
+          <t>2026-06-27T12:54:54.6924037+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1209,7 +1221,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12:47:16.529</t>
+          <t>12:54:54.692</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2732,18 +2744,94 @@
         <v>44</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="4">
+        <v>30</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J47" s="4">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="48">
-      <c r="A48" t="s">
-        <v>109</v>
-      </c>
-      <c r="B48" t="s">
-        <v>110</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="A48" s="4">
+        <v>31</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E48">
-        <v>29</v>
+      <c r="C48" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J48" s="4">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" t="s">
+        <v>114</v>
+      </c>
+      <c r="D50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E50">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T12:56:55+05:30</t>
+    <t>Generated 2026-06-27T12:59:47+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T12:54:54+05:30 (2m0s ago)</t>
+    <t>2026-06-27T12:57:47+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>5</t>
   </si>
   <si>
     <t>Last error</t>
@@ -357,10 +357,16 @@
     <t>12:54:54.692</t>
   </si>
   <si>
+    <t>2026-06-27T12:57:26.7335815+05:30</t>
+  </si>
+  <si>
+    <t>12:57:26.733</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T12:56:55+05:30</t>
+    <t>2026-06-27T12:59:47+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -955,7 +961,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 9m 54s</t>
+          <t>0h 12m 47s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -975,7 +981,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 42m 24s</t>
+          <t>73h 45m 19s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -985,7 +991,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>12:56:55</t>
+          <t>12:59:47</t>
         </is>
       </c>
     </row>
@@ -1042,17 +1048,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>948.0</t>
+          <t>521.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>60275.0</t>
+          <t>60283.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1062,7 +1068,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>647</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1082,7 +1088,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>73h 40m 34s</t>
+          <t>73h 43m 19s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1092,7 +1098,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>12:56:55</t>
+          <t>12:59:47</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1217,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T12:54:54.6924037+05:30</t>
+          <t>2026-06-27T12:57:26.7335815+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1221,7 +1227,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12:54:54.692</t>
+          <t>12:57:26.733</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2820,18 +2826,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="s">
+    <row r="49">
+      <c r="A49" s="4">
+        <v>32</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C49" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E49" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J49" s="4">
+        <v>0</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
         <v>115</v>
       </c>
-      <c r="E50">
-        <v>31</v>
+      <c r="B51" t="s">
+        <v>116</v>
+      </c>
+      <c r="D51" t="s">
+        <v>117</v>
+      </c>
+      <c r="E51">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T12:59:47+05:30</t>
+    <t>Generated 2026-06-27T13:02:14+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T12:57:47+05:30 (2m0s ago)</t>
+    <t>2026-06-27T13:00:14+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t>Last error</t>
@@ -363,10 +363,16 @@
     <t>12:57:26.733</t>
   </si>
   <si>
+    <t>2026-06-27T13:00:14.3831046+05:30</t>
+  </si>
+  <si>
+    <t>13:00:14.383</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T12:59:47+05:30</t>
+    <t>2026-06-27T13:02:14+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -961,7 +967,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 47s</t>
+          <t>0h 15m 13s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -981,7 +987,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 45m 19s</t>
+          <t>73h 47m 44s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -991,7 +997,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>12:59:47</t>
+          <t>13:02:14</t>
         </is>
       </c>
     </row>
@@ -1048,17 +1054,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>521.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>60283.0</t>
+          <t>60285.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1068,7 +1074,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>794</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1088,7 +1094,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>73h 43m 19s</t>
+          <t>73h 45m 44s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1098,7 +1104,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>12:59:47</t>
+          <t>13:02:14</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1223,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T12:57:26.7335815+05:30</t>
+          <t>2026-06-27T13:00:14.3831046+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1227,7 +1233,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12:57:26.733</t>
+          <t>13:00:14.383</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2864,18 +2870,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="s">
+    <row r="50">
+      <c r="A50" s="4">
+        <v>33</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C50" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E50" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J50" s="4">
+        <v>0</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
         <v>117</v>
       </c>
-      <c r="E51">
-        <v>32</v>
+      <c r="B52" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52" t="s">
+        <v>119</v>
+      </c>
+      <c r="E52">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:02:14+05:30</t>
+    <t>Generated 2026-06-27T13:04:46+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:00:14+05:30 (2m0s ago)</t>
+    <t>2026-06-27T13:03:07+05:30 (1m38s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>6</t>
+    <t>9</t>
   </si>
   <si>
     <t>Last error</t>
@@ -369,10 +369,16 @@
     <t>13:00:14.383</t>
   </si>
   <si>
+    <t>2026-06-27T13:02:26.6078418+05:30</t>
+  </si>
+  <si>
+    <t>13:02:26.607</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:02:14+05:30</t>
+    <t>2026-06-27T13:04:46+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -967,7 +973,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 15m 13s</t>
+          <t>0h 17m 45s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -987,7 +993,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 47m 44s</t>
+          <t>73h 50m 4s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -997,7 +1003,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:02:14</t>
+          <t>13:04:46</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1060,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>256.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>60285.0</t>
+          <t>78531.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1074,7 +1080,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>967</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1094,7 +1100,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>73h 45m 44s</t>
+          <t>73h 48m 39s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1104,7 +1110,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:02:14</t>
+          <t>13:04:46</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1229,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T13:00:14.3831046+05:30</t>
+          <t>2026-06-27T13:02:26.6078418+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1233,7 +1239,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13:00:14.383</t>
+          <t>13:02:26.607</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2908,18 +2914,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="s">
+    <row r="51">
+      <c r="A51" s="4">
+        <v>34</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C51" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E51" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J51" s="4">
+        <v>0</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
         <v>119</v>
       </c>
-      <c r="E52">
-        <v>33</v>
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="D53" t="s">
+        <v>121</v>
+      </c>
+      <c r="E53">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:04:46+05:30</t>
+    <t>Generated 2026-06-27T13:05:07+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:03:07+05:30 (1m38s ago)</t>
+    <t>2026-06-27T13:03:07+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -378,7 +378,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:04:46+05:30</t>
+    <t>2026-06-27T13:05:07+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -973,7 +973,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 45s</t>
+          <t>0h 18m 6s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 50m 4s</t>
+          <t>73h 50m 29s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:04:46</t>
+          <t>13:05:07</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>256.0</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>78531.0</t>
+          <t>78521.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:04:46</t>
+          <t>13:05:07</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:05:07+05:30</t>
+    <t>Generated 2026-06-27T13:07:48+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:03:07+05:30 (2m0s ago)</t>
+    <t>2026-06-27T13:07:47+05:30 (0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>9</t>
+    <t>12</t>
   </si>
   <si>
     <t>Last error</t>
@@ -375,10 +375,22 @@
     <t>13:02:26.607</t>
   </si>
   <si>
+    <t>2026-06-27T13:05:13.413566+05:30</t>
+  </si>
+  <si>
+    <t>13:05:13.413</t>
+  </si>
+  <si>
+    <t>2026-06-27T13:07:47.8377066+05:30</t>
+  </si>
+  <si>
+    <t>13:07:47.837</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:05:07+05:30</t>
+    <t>2026-06-27T13:07:48+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -973,7 +985,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 18m 6s</t>
+          <t>0h 20m 48s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -993,7 +1005,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 50m 29s</t>
+          <t>73h 51m 14s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1003,7 +1015,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:05:07</t>
+          <t>13:07:48</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1072,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>78521.0</t>
+          <t>345317.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1080,7 +1092,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1100,7 +1112,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>73h 48m 39s</t>
+          <t>73h 50m 54s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1110,7 +1122,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:05:07</t>
+          <t>13:07:48</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1241,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T13:02:26.6078418+05:30</t>
+          <t>2026-06-27T13:07:47.8377066+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1239,7 +1251,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13:02:26.607</t>
+          <t>13:07:47.837</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2952,18 +2964,94 @@
         <v>44</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="4">
+        <v>35</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J52" s="4">
+        <v>0</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="53">
-      <c r="A53" t="s">
-        <v>119</v>
-      </c>
-      <c r="B53" t="s">
-        <v>120</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="A53" s="4">
+        <v>36</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E53">
-        <v>34</v>
+      <c r="C53" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J53" s="4">
+        <v>0</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" t="s">
+        <v>124</v>
+      </c>
+      <c r="D55" t="s">
+        <v>125</v>
+      </c>
+      <c r="E55">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:07:48+05:30</t>
+    <t>Generated 2026-06-27T13:10:06+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:07:47+05:30 (0s ago)</t>
+    <t>2026-06-27T13:08:23+05:30 (1m43s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>12</t>
+    <t>14</t>
   </si>
   <si>
     <t>Last error</t>
@@ -390,7 +390,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:07:48+05:30</t>
+    <t>2026-06-27T13:10:06+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -985,7 +985,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 20m 48s</t>
+          <t>0h 23m 5s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 51m 14s</t>
+          <t>73h 53m 19s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:07:48</t>
+          <t>13:10:06</t>
         </is>
       </c>
     </row>
@@ -1072,17 +1072,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>2957.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>345317.0</t>
+          <t>60287.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>11393</t>
+          <t>15868</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>73h 50m 54s</t>
+          <t>73h 51m 39s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:07:48</t>
+          <t>13:10:06</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:10:06+05:30</t>
+    <t>Generated 2026-06-27T13:10:23+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:08:23+05:30 (1m43s ago)</t>
+    <t>2026-06-27T13:10:13+05:30 (10s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>Last error</t>
@@ -387,10 +387,16 @@
     <t>13:07:47.837</t>
   </si>
   <si>
+    <t>2026-06-27T13:10:13.3773365+05:30</t>
+  </si>
+  <si>
+    <t>13:10:13.377</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:10:06+05:30</t>
+    <t>2026-06-27T13:10:23+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -985,7 +991,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 23m 5s</t>
+          <t>0h 23m 22s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1005,7 +1011,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 53m 19s</t>
+          <t>73h 53m 39s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1015,7 +1021,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:10:06</t>
+          <t>13:10:23</t>
         </is>
       </c>
     </row>
@@ -1072,17 +1078,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2957.0</t>
+          <t>1432.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>60287.0</t>
+          <t>99537.6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>15868</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1092,7 +1098,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1112,7 +1118,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>73h 51m 39s</t>
+          <t>73h 53m 29s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1122,7 +1128,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:10:06</t>
+          <t>13:10:23</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1247,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T13:07:47.8377066+05:30</t>
+          <t>2026-06-27T13:10:13.3773365+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1251,7 +1257,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13:07:47.837</t>
+          <t>13:10:13.377</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3040,18 +3046,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="s">
+    <row r="54">
+      <c r="A54" s="4">
+        <v>37</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C54" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E54" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J54" s="4">
+        <v>0</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
         <v>125</v>
       </c>
-      <c r="E55">
-        <v>36</v>
+      <c r="B56" t="s">
+        <v>126</v>
+      </c>
+      <c r="D56" t="s">
+        <v>127</v>
+      </c>
+      <c r="E56">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:10:23+05:30</t>
+    <t>Generated 2026-06-27T13:12:13+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:10:13+05:30 (10s ago)</t>
+    <t>2026-06-27T13:10:55+05:30 (1m17s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>15</t>
+    <t>17</t>
   </si>
   <si>
     <t>Last error</t>
@@ -396,7 +396,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:10:23+05:30</t>
+    <t>2026-06-27T13:12:13+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -991,7 +991,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 23m 22s</t>
+          <t>0h 25m 12s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 53m 39s</t>
+          <t>73h 55m 29s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:10:23</t>
+          <t>13:12:13</t>
         </is>
       </c>
     </row>
@@ -1078,17 +1078,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1432.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>99537.6</t>
+          <t>104665.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>17279</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>73h 53m 29s</t>
+          <t>73h 54m 9s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:10:23</t>
+          <t>13:12:13</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:12:13+05:30</t>
+    <t>Generated 2026-06-27T13:12:31+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:10:55+05:30 (1m17s ago)</t>
+    <t>2026-06-27T13:12:26+05:30 (4s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>Last error</t>
@@ -393,10 +393,16 @@
     <t>13:10:13.377</t>
   </si>
   <si>
+    <t>2026-06-27T13:12:26.7086266+05:30</t>
+  </si>
+  <si>
+    <t>13:12:26.708</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:12:13+05:30</t>
+    <t>2026-06-27T13:12:31+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -991,7 +997,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 25m 12s</t>
+          <t>0h 25m 30s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1011,7 +1017,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 55m 29s</t>
+          <t>73h 55m 44s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1021,7 +1027,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:12:13</t>
+          <t>13:12:31</t>
         </is>
       </c>
     </row>
@@ -1078,17 +1084,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>2523.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>104665.0</t>
+          <t>101296.2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>17279</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1128,7 +1134,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:12:13</t>
+          <t>13:12:31</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1253,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T13:10:13.3773365+05:30</t>
+          <t>2026-06-27T13:12:26.7086266+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1257,7 +1263,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13:10:13.377</t>
+          <t>13:12:26.708</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3084,18 +3090,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="s">
+    <row r="55">
+      <c r="A55" s="4">
+        <v>38</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C55" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E55" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J55" s="4">
+        <v>0</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
         <v>127</v>
       </c>
-      <c r="E56">
-        <v>37</v>
+      <c r="B57" t="s">
+        <v>128</v>
+      </c>
+      <c r="D57" t="s">
+        <v>129</v>
+      </c>
+      <c r="E57">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:12:31+05:30</t>
+    <t>Generated 2026-06-27T13:12:56+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:12:26+05:30 (4s ago)</t>
+    <t>2026-06-27T13:12:44+05:30 (11s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>Last error</t>
@@ -402,7 +402,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:12:31+05:30</t>
+    <t>2026-06-27T13:12:56+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -997,7 +997,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 25m 30s</t>
+          <t>0h 25m 55s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 55m 44s</t>
+          <t>73h 56m 9s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:12:31</t>
+          <t>13:12:56</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2523.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>101296.2</t>
+          <t>114732.8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>17656</t>
+          <t>18300</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>73h 54m 9s</t>
+          <t>73h 55m 59s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:12:31</t>
+          <t>13:12:56</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:12:56+05:30</t>
+    <t>Generated 2026-06-27T13:14:45+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:12:44+05:30 (11s ago)</t>
+    <t>2026-06-27T13:13:41+05:30 (1m3s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>19</t>
+    <t>22</t>
   </si>
   <si>
     <t>Last error</t>
@@ -399,10 +399,16 @@
     <t>13:12:26.708</t>
   </si>
   <si>
+    <t>2026-06-27T13:13:41.5065792+05:30</t>
+  </si>
+  <si>
+    <t>13:13:41.506</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:12:56+05:30</t>
+    <t>2026-06-27T13:14:45+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -997,7 +1003,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 25m 55s</t>
+          <t>0h 27m 44s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1017,7 +1023,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 56m 9s</t>
+          <t>73h 57m 59s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1027,7 +1033,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:12:56</t>
+          <t>13:14:45</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1090,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>114732.8</t>
+          <t>135735.8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>20990</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1104,7 +1110,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1124,7 +1130,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>73h 55m 59s</t>
+          <t>73h 56m 54s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1134,7 +1140,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:12:56</t>
+          <t>13:14:45</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1259,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T13:12:26.7086266+05:30</t>
+          <t>2026-06-27T13:13:41.5065792+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1263,7 +1269,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13:12:26.708</t>
+          <t>13:13:41.506</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3128,18 +3134,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="s">
+    <row r="56">
+      <c r="A56" s="4">
+        <v>39</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C56" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E56" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J56" s="4">
+        <v>0</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
         <v>129</v>
       </c>
-      <c r="E57">
-        <v>38</v>
+      <c r="B58" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" t="s">
+        <v>131</v>
+      </c>
+      <c r="E58">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:14:45+05:30</t>
+    <t>Generated 2026-06-27T13:15:01+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:13:41+05:30 (1m3s ago)</t>
+    <t>2026-06-27T13:13:41+05:30 (1m19s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -408,7 +408,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:14:45+05:30</t>
+    <t>2026-06-27T13:15:01+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 27m 44s</t>
+          <t>0h 28m 0s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 57m 59s</t>
+          <t>73h 58m 14s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:14:45</t>
+          <t>13:15:01</t>
         </is>
       </c>
     </row>
@@ -1090,17 +1090,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>767.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>135735.8</t>
+          <t>103349.8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>20990</t>
+          <t>21380</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:14:45</t>
+          <t>13:15:01</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:15:01+05:30</t>
+    <t>Generated 2026-06-27T13:15:22+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:13:41+05:30 (1m19s ago)</t>
+    <t>2026-06-27T13:15:07+05:30 (15s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>Last error</t>
@@ -405,10 +405,16 @@
     <t>13:13:41.506</t>
   </si>
   <si>
+    <t>2026-06-27T13:15:07.0179629+05:30</t>
+  </si>
+  <si>
+    <t>13:15:07.017</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:15:01+05:30</t>
+    <t>2026-06-27T13:15:22+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -968,7 +974,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>server+agent</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1003,7 +1009,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 28m 0s</t>
+          <t>0h 28m 21s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1023,7 +1029,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 58m 14s</t>
+          <t>73h 58m 34s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1033,7 +1039,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:15:01</t>
+          <t>13:15:22</t>
         </is>
       </c>
     </row>
@@ -1090,17 +1096,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>767.0</t>
+          <t>855.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>103349.8</t>
+          <t>114993.8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>21909</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1140,7 +1146,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:15:01</t>
+          <t>13:15:22</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1265,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T13:13:41.5065792+05:30</t>
+          <t>2026-06-27T13:15:07.0179629+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1269,7 +1275,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13:13:41.506</t>
+          <t>13:15:07.017</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3172,18 +3178,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="s">
+    <row r="57">
+      <c r="A57" s="4">
+        <v>40</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C57" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E57" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J57" s="4">
+        <v>0</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
         <v>131</v>
       </c>
-      <c r="E58">
-        <v>39</v>
+      <c r="B59" t="s">
+        <v>132</v>
+      </c>
+      <c r="D59" t="s">
+        <v>133</v>
+      </c>
+      <c r="E59">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:15:22+05:30</t>
+    <t>Generated 2026-06-27T13:15:41+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:15:07+05:30 (15s ago)</t>
+    <t>2026-06-27T13:15:07+05:30 (34s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -414,7 +414,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:15:22+05:30</t>
+    <t>2026-06-27T13:15:41+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 28m 21s</t>
+          <t>0h 28m 40s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:15:22</t>
+          <t>13:15:41</t>
         </is>
       </c>
     </row>
@@ -1096,17 +1096,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>855.0</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>114993.8</t>
+          <t>102062.2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>21909</t>
+          <t>22366</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:15:22</t>
+          <t>13:15:41</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:15:41+05:30</t>
+    <t>Generated 2026-06-27T13:27:45+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:15:07+05:30 (34s ago)</t>
+    <t>2026-06-27T13:25:38+05:30 (2m7s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>23</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -411,10 +411,16 @@
     <t>13:15:07.017</t>
   </si>
   <si>
+    <t>2026-06-27T13:25:38.0396606+05:30</t>
+  </si>
+  <si>
+    <t>13:25:38.039</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:15:41+05:30</t>
+    <t>2026-06-27T13:27:45+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -974,7 +980,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>server+agent</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1009,12 +1015,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 28m 40s</t>
+          <t>0h 2m 23s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-27 12:47:00</t>
+          <t>2026-06-27 13:25:21</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1024,12 +1030,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-27 12:47:00</t>
+          <t>2026-06-27 13:25:21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>73h 58m 34s</t>
+          <t>74h 5m 39s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1039,7 +1045,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:15:41</t>
+          <t>13:27:45</t>
         </is>
       </c>
     </row>
@@ -1096,17 +1102,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>102062.2</t>
+          <t>104259.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1116,7 +1122,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1131,12 +1137,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-27 12:47:00</t>
+          <t>2026-06-27 13:25:21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>73h 56m 54s</t>
+          <t>74h 3m 39s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1146,7 +1152,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:15:41</t>
+          <t>13:27:45</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1271,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T13:15:07.0179629+05:30</t>
+          <t>2026-06-27T13:25:38.0396606+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1275,7 +1281,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13:15:07.017</t>
+          <t>13:25:38.039</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3216,18 +3222,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="s">
+    <row r="58">
+      <c r="A58" s="4">
+        <v>41</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C58" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E58" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J58" s="4">
+        <v>0</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
         <v>133</v>
       </c>
-      <c r="E59">
-        <v>40</v>
+      <c r="B60" t="s">
+        <v>134</v>
+      </c>
+      <c r="D60" t="s">
+        <v>135</v>
+      </c>
+      <c r="E60">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:27:45+05:30</t>
+    <t>Generated 2026-06-27T13:33:04+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:25:38+05:30 (2m7s ago)</t>
+    <t>2026-06-27T13:31:04+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>Last error</t>
@@ -417,10 +417,16 @@
     <t>13:25:38.039</t>
   </si>
   <si>
+    <t>2026-06-27T13:30:46.6820172+05:30</t>
+  </si>
+  <si>
+    <t>13:30:46.682</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:27:45+05:30</t>
+    <t>2026-06-27T13:33:04+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1015,7 +1021,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 23s</t>
+          <t>0h 7m 42s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1035,7 +1041,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>74h 5m 39s</t>
+          <t>74h 7m 4s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1045,7 +1051,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:27:45</t>
+          <t>13:33:04</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1113,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>104259.0</t>
+          <t>109274.8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1122,7 +1128,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>342</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1142,7 +1148,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>74h 3m 39s</t>
+          <t>74h 6m 34s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1152,7 +1158,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:27:45</t>
+          <t>13:33:04</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1277,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T13:25:38.0396606+05:30</t>
+          <t>2026-06-27T13:30:46.6820172+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1281,7 +1287,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13:25:38.039</t>
+          <t>13:30:46.682</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3260,18 +3266,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="s">
+    <row r="59">
+      <c r="A59" s="4">
+        <v>42</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C59" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E59" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J59" s="4">
+        <v>0</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
         <v>135</v>
       </c>
-      <c r="E60">
-        <v>41</v>
+      <c r="B61" t="s">
+        <v>136</v>
+      </c>
+      <c r="D61" t="s">
+        <v>137</v>
+      </c>
+      <c r="E61">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:33:04+05:30</t>
+    <t>Generated 2026-06-27T13:40:18+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:31:04+05:30 (2m0s ago)</t>
+    <t>2026-06-27T13:38:11+05:30 (2m7s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -423,10 +423,22 @@
     <t>13:30:46.682</t>
   </si>
   <si>
+    <t>2026-06-27T13:35:46.6288082+05:30</t>
+  </si>
+  <si>
+    <t>13:35:46.628</t>
+  </si>
+  <si>
+    <t>2026-06-27T13:38:11.0595449+05:30</t>
+  </si>
+  <si>
+    <t>13:38:11.059</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:33:04+05:30</t>
+    <t>2026-06-27T13:40:18+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1021,12 +1033,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 42s</t>
+          <t>0h 2m 22s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-27 13:25:21</t>
+          <t>2026-06-27 13:37:56</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1036,12 +1048,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-27 13:25:21</t>
+          <t>2026-06-27 13:37:56</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>74h 7m 4s</t>
+          <t>74h 14m 4s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1051,7 +1063,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:33:04</t>
+          <t>13:40:18</t>
         </is>
       </c>
     </row>
@@ -1108,17 +1120,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>109274.8</t>
+          <t>125127.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1128,7 +1140,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1143,12 +1155,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-27 13:25:21</t>
+          <t>2026-06-27 13:37:56</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>74h 6m 34s</t>
+          <t>74h 12m 4s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1158,7 +1170,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:33:04</t>
+          <t>13:40:18</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1289,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27T13:30:46.6820172+05:30</t>
+          <t>2026-06-27T13:38:11.0595449+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1287,7 +1299,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13:30:46.682</t>
+          <t>13:38:11.059</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3304,18 +3316,94 @@
         <v>44</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="4">
+        <v>43</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J60" s="4">
+        <v>0</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" t="s">
-        <v>135</v>
-      </c>
-      <c r="B61" t="s">
-        <v>136</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="A61" s="4">
+        <v>44</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E61">
-        <v>42</v>
+      <c r="C61" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J61" s="4">
+        <v>0</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" t="s">
+        <v>140</v>
+      </c>
+      <c r="D63" t="s">
+        <v>141</v>
+      </c>
+      <c r="E63">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:40:18+05:30</t>
+    <t>Generated 2026-06-27T13:45:36+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:38:11+05:30 (2m7s ago)</t>
+    <t>2026-06-27T13:43:36+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>Last error</t>
@@ -435,10 +435,16 @@
     <t>13:38:11.059</t>
   </si>
   <si>
+    <t>2026-06-27T13:43:19.5232068+05:30</t>
+  </si>
+  <si>
+    <t>13:43:19.523</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:40:18+05:30</t>
+    <t>2026-06-27T13:45:36+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1033,7 +1039,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 22s</t>
+          <t>0h 7m 40s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1053,7 +1059,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>74h 14m 4s</t>
+          <t>74h 19m 19s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1063,7 +1069,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:40:18</t>
+          <t>13:45:36</t>
         </is>
       </c>
     </row>
@@ -1120,17 +1126,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>125127.0</t>
+          <t>125133.4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1140,7 +1146,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>341</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1160,7 +1166,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>74h 12m 4s</t>
+          <t>74h 17m 19s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1170,217 +1176,324 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:40:18</t>
+          <t>13:45:36</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>── LATEST GITHUB ELECTION EVENT ──</t>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t/>
+          <t>PuneetU-EB6LMJD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t/>
+          <t>192.168.0.164</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t/>
+          <t>43.247.40.101</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t/>
+          <t>windows</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>amd64</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t/>
+          <t>10.0.64</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t/>
+          <t>agent</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t/>
+          <t>websocket</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t/>
+          <t>good</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t/>
+          <t>15176.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t/>
+          <t>107490.8</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.5</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t/>
+          <t>213</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t/>
+          <t>—</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t/>
+          <t>Jun 17 10:41 PM</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t/>
+          <t>—</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t/>
+          <t>3h 20m 1s</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t/>
+          <t>13:45:36</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>── LATEST GITHUB ELECTION EVENT ──</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>[renewed]</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-27T13:38:11.0595449+05:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-27T13:43:19.5232068+05:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>13:38:11.059</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>13:43:19.523</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>renewed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>github</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>SAATHII-TB-b19900d6</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>SAATHII-TB</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>SAATHII-TB-b19900d6</t>
         </is>
       </c>
-      <c r="J5">
+      <c r="J6">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>renewed</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3392,18 +3505,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="s">
+    <row r="62">
+      <c r="A62" s="4">
+        <v>45</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C62" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E62" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J62" s="4">
+        <v>0</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
         <v>141</v>
       </c>
-      <c r="E63">
-        <v>44</v>
+      <c r="B64" t="s">
+        <v>142</v>
+      </c>
+      <c r="D64" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:45:36+05:30</t>
+    <t>Generated 2026-06-27T13:50:31+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:43:36+05:30 (2m0s ago)</t>
+    <t>2026-06-27T13:48:50+05:30 (1m40s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>6</t>
   </si>
   <si>
     <t>Last error</t>
@@ -441,10 +441,16 @@
     <t>13:43:19.523</t>
   </si>
   <si>
+    <t>2026-06-27T13:48:19.8539374+05:30</t>
+  </si>
+  <si>
+    <t>13:48:19.853</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:45:36+05:30</t>
+    <t>2026-06-27T13:50:31+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1039,7 +1045,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 40s</t>
+          <t>0h 12m 35s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1059,7 +1065,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>74h 19m 19s</t>
+          <t>74h 24m 14s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1069,7 +1075,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:45:36</t>
+          <t>13:50:31</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1132,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>125133.4</t>
+          <t>24425.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1146,7 +1152,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>655</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1166,7 +1172,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>74h 17m 19s</t>
+          <t>74h 22m 34s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1176,7 +1182,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:45:36</t>
+          <t>13:50:31</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1214,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>amd64</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1218,42 +1224,42 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>disconnected</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>websocket</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>15176.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>107490.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1263,7 +1269,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Jun 17 10:41 PM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1273,7 +1279,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>3h 20m 1s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1283,7 +1289,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>13:45:36</t>
+          <t>13:50:31</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1408,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-27T13:43:19.5232068+05:30</t>
+          <t>2026-06-27T13:48:19.8539374+05:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1412,7 +1418,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13:43:19.523</t>
+          <t>13:48:19.853</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3543,18 +3549,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="s">
+    <row r="63">
+      <c r="A63" s="4">
+        <v>46</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C63" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E63" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J63" s="4">
+        <v>0</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
         <v>143</v>
       </c>
-      <c r="E64">
-        <v>45</v>
+      <c r="B65" t="s">
+        <v>144</v>
+      </c>
+      <c r="D65" t="s">
+        <v>145</v>
+      </c>
+      <c r="E65">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:50:31+05:30</t>
+    <t>Generated 2026-06-27T13:50:50+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:48:50+05:30 (1m40s ago)</t>
+    <t>2026-06-27T13:48:50+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -450,7 +450,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:50:31+05:30</t>
+    <t>2026-06-27T13:50:50+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 35s</t>
+          <t>0h 12m 54s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>74h 24m 14s</t>
+          <t>74h 24m 34s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:50:31</t>
+          <t>13:50:50</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:50:31</t>
+          <t>13:50:50</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>13:50:31</t>
+          <t>13:50:50</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:50:50+05:30</t>
+    <t>Generated 2026-06-27T13:55:34+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:48:50+05:30 (2m0s ago)</t>
+    <t>2026-06-27T13:53:56+05:30 (1m37s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>6</t>
+    <t>9</t>
   </si>
   <si>
     <t>Last error</t>
@@ -447,10 +447,16 @@
     <t>13:48:19.853</t>
   </si>
   <si>
+    <t>2026-06-27T13:53:19.5285452+05:30</t>
+  </si>
+  <si>
+    <t>13:53:19.528</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:50:50+05:30</t>
+    <t>2026-06-27T13:55:34+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1045,7 +1051,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 54s</t>
+          <t>0h 17m 38s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1065,7 +1071,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>74h 24m 34s</t>
+          <t>74h 29m 19s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1075,7 +1081,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:50:50</t>
+          <t>13:55:34</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1138,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1142,7 +1148,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1152,7 +1158,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>961</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1172,7 +1178,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>74h 22m 34s</t>
+          <t>74h 27m 39s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1182,7 +1188,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:50:50</t>
+          <t>13:55:34</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1295,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>13:50:50</t>
+          <t>13:55:34</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1414,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:19.8539374+05:30</t>
+          <t>2026-06-27T13:53:19.5285452+05:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1418,7 +1424,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13:48:19.853</t>
+          <t>13:53:19.528</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3587,18 +3593,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="s">
+    <row r="64">
+      <c r="A64" s="4">
+        <v>47</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C64" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E64" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J64" s="4">
+        <v>0</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
         <v>145</v>
       </c>
-      <c r="E65">
-        <v>46</v>
+      <c r="B66" t="s">
+        <v>146</v>
+      </c>
+      <c r="D66" t="s">
+        <v>147</v>
+      </c>
+      <c r="E66">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-27.xlsx
+++ b/report-2026-06-27.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-27T13:55:34+05:30</t>
+    <t>Generated 2026-06-27T13:55:56+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-27T13:53:56+05:30 (1m37s ago)</t>
+    <t>2026-06-27T13:53:56+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -456,7 +456,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-27T13:55:34+05:30</t>
+    <t>2026-06-27T13:55:56+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 38s</t>
+          <t>0h 18m 0s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>74h 29m 19s</t>
+          <t>74h 29m 39s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:55:34</t>
+          <t>13:55:56</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:55:34</t>
+          <t>13:55:56</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>13:55:34</t>
+          <t>13:55:56</t>
         </is>
       </c>
     </row>
